--- a/Projects/VoortoetsAGT/cases/UitkerkDens/UitkerkDens.xlsx
+++ b/Projects/VoortoetsAGT/cases/UitkerkDens/UitkerkDens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Theo/GRWMODELS/python/mf6lab/Projects/VoortoetsAGT/cases/UitkerkDens/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B34DB8C-7B55-CE44-B1EE-5BF4A400FE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE54050-4781-D647-BC87-72E4F1C8F9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4040" yWindow="960" windowWidth="30600" windowHeight="19860" tabRatio="751" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4040" yWindow="960" windowWidth="30600" windowHeight="19860" tabRatio="751" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAM" sheetId="1" r:id="rId1"/>
@@ -7922,7 +7922,7 @@
         <v>26</v>
       </c>
       <c r="C425">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.15">
